--- a/ig/TEST-SUPPLEMENT/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250828120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-28T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -228,7 +228,7 @@
     <t>035</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement d'organes</t>
+    <t>Coordination hospitalière de prélèvement d'organe</t>
   </si>
   <si>
     <t>037</t>
@@ -3174,19 +3174,19 @@
     <t>594</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement de tissus</t>
+    <t>Coordination hospitalière de prélèvement de tissu</t>
   </si>
   <si>
     <t>595</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement de tissus pédiatrique</t>
+    <t>Coordination hospitalière de prélèvement de tissu pédiatrique</t>
   </si>
   <si>
     <t>596</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement d’organes pédiatrique</t>
+    <t>Coordination hospitalière de prélèvement d’organe pédiatrique</t>
   </si>
   <si>
     <t>597</t>
